--- a/output/pdf_financials_xlsx/CDN.xlsx
+++ b/output/pdf_financials_xlsx/CDN.xlsx
@@ -1978,13 +1978,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.677475</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.977097</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.100568</v>
       </c>
     </row>
     <row r="93">
@@ -3129,7 +3129,11 @@
           <t>Reserves (note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>1.677475</v>
       </c>

--- a/output/pdf_financials_xlsx/CDN.xlsx
+++ b/output/pdf_financials_xlsx/CDN.xlsx
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.1857</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.005185</v>
       </c>
     </row>
     <row r="13">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.932587</v>
+        <v>-2.118287</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.473504</v>
+        <v>-2.478689</v>
       </c>
     </row>
     <row r="28">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.923867</v>
+        <v>-2.109567</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.467264</v>
+        <v>-2.472449</v>
       </c>
     </row>
     <row r="30">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.498574</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.370548</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.89334</v>
       </c>
     </row>
     <row r="35">
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.964098</v>
+        <v>1.462672</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2.233895</v>
+        <v>2.604443</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.948376</v>
+        <v>1.841716</v>
       </c>
     </row>
     <row r="37">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.525655</v>
+        <v>0.027081</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.407022</v>
+        <v>0.036474</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.929592</v>
+        <v>0.036252</v>
       </c>
     </row>
     <row r="49">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">

--- a/output/pdf_financials_xlsx/CDN.xlsx
+++ b/output/pdf_financials_xlsx/CDN.xlsx
@@ -2331,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-0.08505</v>
       </c>
     </row>
     <row r="115">
@@ -2344,10 +2344,10 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0.027973</v>
+        <v>0.307263</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0.47098</v>
+        <v>1.49404</v>
       </c>
     </row>
     <row r="116">
@@ -4655,7 +4655,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -4684,7 +4688,11 @@
           <t>Purchase of marketable securites</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
